--- a/artfynd/A 1912-2023 artfynd.xlsx
+++ b/artfynd/A 1912-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1912-2023 artfynd.xlsx
+++ b/artfynd/A 1912-2023 artfynd.xlsx
@@ -2360,7 +2360,7 @@
         <v>126859596</v>
       </c>
       <c r="B15" t="n">
-        <v>91699</v>
+        <v>91773</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>126858689</v>
       </c>
       <c r="B16" t="n">
-        <v>79450</v>
+        <v>79481</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>126859418</v>
       </c>
       <c r="B19" t="n">
-        <v>91298</v>
+        <v>91372</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>126858508</v>
       </c>
       <c r="B20" t="n">
-        <v>82792</v>
+        <v>82852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 1912-2023 artfynd.xlsx
+++ b/artfynd/A 1912-2023 artfynd.xlsx
@@ -2360,7 +2360,7 @@
         <v>126859596</v>
       </c>
       <c r="B15" t="n">
-        <v>91773</v>
+        <v>91779</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>126858689</v>
       </c>
       <c r="B16" t="n">
-        <v>79481</v>
+        <v>79484</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>126859418</v>
       </c>
       <c r="B19" t="n">
-        <v>91372</v>
+        <v>91378</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>126858508</v>
       </c>
       <c r="B20" t="n">
-        <v>82852</v>
+        <v>82855</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 1912-2023 artfynd.xlsx
+++ b/artfynd/A 1912-2023 artfynd.xlsx
@@ -2761,10 +2761,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126859410</v>
+        <v>126859418</v>
       </c>
       <c r="B18" t="n">
-        <v>8458</v>
+        <v>91378</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2772,32 +2772,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101987</v>
+        <v>5321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aspvedborre</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Heteroborips cryptographus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ratzeburg, 1837)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2898,10 +2892,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126859418</v>
+        <v>126859410</v>
       </c>
       <c r="B19" t="n">
-        <v>91378</v>
+        <v>8458</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2909,26 +2903,32 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5321</v>
+        <v>101987</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Aspvedborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Heteroborips cryptographus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ratzeburg, 1837)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>

--- a/artfynd/A 1912-2023 artfynd.xlsx
+++ b/artfynd/A 1912-2023 artfynd.xlsx
@@ -2360,7 +2360,7 @@
         <v>126859596</v>
       </c>
       <c r="B15" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2488,10 +2488,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126858689</v>
+        <v>126859377</v>
       </c>
       <c r="B16" t="n">
-        <v>79484</v>
+        <v>40036</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2499,26 +2499,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1797</v>
+        <v>101166</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2526,10 +2532,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509182</v>
+        <v>509208</v>
       </c>
       <c r="R16" t="n">
-        <v>6663541</v>
+        <v>6663371</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2561,7 +2567,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2571,7 +2577,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2584,29 +2590,24 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2624,10 +2625,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126859377</v>
+        <v>126858689</v>
       </c>
       <c r="B17" t="n">
-        <v>40036</v>
+        <v>79484</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2635,32 +2636,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101166</v>
+        <v>1797</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2668,10 +2663,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509208</v>
+        <v>509182</v>
       </c>
       <c r="R17" t="n">
-        <v>6663371</v>
+        <v>6663541</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2703,7 +2698,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2713,7 +2708,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2726,24 +2721,29 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2764,7 +2764,7 @@
         <v>126859418</v>
       </c>
       <c r="B18" t="n">
-        <v>91378</v>
+        <v>91379</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 1912-2023 artfynd.xlsx
+++ b/artfynd/A 1912-2023 artfynd.xlsx
@@ -2761,10 +2761,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126859418</v>
+        <v>126859410</v>
       </c>
       <c r="B18" t="n">
-        <v>91379</v>
+        <v>8458</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2772,26 +2772,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5321</v>
+        <v>101987</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Aspvedborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Heteroborips cryptographus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ratzeburg, 1837)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2892,10 +2898,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126859410</v>
+        <v>126859418</v>
       </c>
       <c r="B19" t="n">
-        <v>8458</v>
+        <v>91379</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2903,32 +2909,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101987</v>
+        <v>5321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aspvedborre</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Heteroborips cryptographus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ratzeburg, 1837)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>

--- a/artfynd/A 1912-2023 artfynd.xlsx
+++ b/artfynd/A 1912-2023 artfynd.xlsx
@@ -2488,10 +2488,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126859377</v>
+        <v>126858689</v>
       </c>
       <c r="B16" t="n">
-        <v>40036</v>
+        <v>79484</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2499,32 +2499,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101166</v>
+        <v>1797</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2532,10 +2526,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509208</v>
+        <v>509182</v>
       </c>
       <c r="R16" t="n">
-        <v>6663371</v>
+        <v>6663541</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2567,7 +2561,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2577,7 +2571,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2590,24 +2584,29 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2625,10 +2624,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126858689</v>
+        <v>126859377</v>
       </c>
       <c r="B17" t="n">
-        <v>79484</v>
+        <v>40036</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2636,26 +2635,32 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1797</v>
+        <v>101166</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2663,10 +2668,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509182</v>
+        <v>509208</v>
       </c>
       <c r="R17" t="n">
-        <v>6663541</v>
+        <v>6663371</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2698,7 +2703,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2708,7 +2713,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2721,29 +2726,24 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126859410</v>
+        <v>126859418</v>
       </c>
       <c r="B18" t="n">
-        <v>8458</v>
+        <v>91379</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2772,32 +2772,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101987</v>
+        <v>5321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aspvedborre</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Heteroborips cryptographus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ratzeburg, 1837)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2898,10 +2892,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126859418</v>
+        <v>126859410</v>
       </c>
       <c r="B19" t="n">
-        <v>91379</v>
+        <v>8458</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2909,26 +2903,32 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5321</v>
+        <v>101987</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Aspvedborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Heteroborips cryptographus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ratzeburg, 1837)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>

--- a/artfynd/A 1912-2023 artfynd.xlsx
+++ b/artfynd/A 1912-2023 artfynd.xlsx
@@ -2360,7 +2360,7 @@
         <v>126859596</v>
       </c>
       <c r="B15" t="n">
-        <v>91780</v>
+        <v>91784</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>126858689</v>
       </c>
       <c r="B16" t="n">
-        <v>79484</v>
+        <v>79488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>126859377</v>
       </c>
       <c r="B17" t="n">
-        <v>40036</v>
+        <v>40040</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>126859418</v>
       </c>
       <c r="B18" t="n">
-        <v>91379</v>
+        <v>91383</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>126859410</v>
       </c>
       <c r="B19" t="n">
-        <v>8458</v>
+        <v>8461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>126858508</v>
       </c>
       <c r="B20" t="n">
-        <v>82855</v>
+        <v>82859</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 1912-2023 artfynd.xlsx
+++ b/artfynd/A 1912-2023 artfynd.xlsx
@@ -2488,10 +2488,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126858689</v>
+        <v>126859377</v>
       </c>
       <c r="B16" t="n">
-        <v>79488</v>
+        <v>40040</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2499,26 +2499,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1797</v>
+        <v>101166</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2526,10 +2532,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509182</v>
+        <v>509208</v>
       </c>
       <c r="R16" t="n">
-        <v>6663541</v>
+        <v>6663371</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2561,7 +2567,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2571,7 +2577,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2584,29 +2590,24 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2624,10 +2625,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126859377</v>
+        <v>126858689</v>
       </c>
       <c r="B17" t="n">
-        <v>40040</v>
+        <v>79488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2635,32 +2636,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101166</v>
+        <v>1797</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2668,10 +2663,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509208</v>
+        <v>509182</v>
       </c>
       <c r="R17" t="n">
-        <v>6663371</v>
+        <v>6663541</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2703,7 +2698,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2713,7 +2708,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2726,24 +2721,29 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 1912-2023 artfynd.xlsx
+++ b/artfynd/A 1912-2023 artfynd.xlsx
@@ -2488,10 +2488,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126859377</v>
+        <v>126858689</v>
       </c>
       <c r="B16" t="n">
-        <v>40040</v>
+        <v>79488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2499,32 +2499,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101166</v>
+        <v>1797</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2532,10 +2526,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509208</v>
+        <v>509182</v>
       </c>
       <c r="R16" t="n">
-        <v>6663371</v>
+        <v>6663541</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2567,7 +2561,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2577,7 +2571,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2590,24 +2584,29 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2625,10 +2624,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126858689</v>
+        <v>126859377</v>
       </c>
       <c r="B17" t="n">
-        <v>79488</v>
+        <v>40040</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2636,26 +2635,32 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1797</v>
+        <v>101166</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2663,10 +2668,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509182</v>
+        <v>509208</v>
       </c>
       <c r="R17" t="n">
-        <v>6663541</v>
+        <v>6663371</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2698,7 +2703,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2708,7 +2713,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2721,29 +2726,24 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 1912-2023 artfynd.xlsx
+++ b/artfynd/A 1912-2023 artfynd.xlsx
@@ -2360,7 +2360,7 @@
         <v>126859596</v>
       </c>
       <c r="B15" t="n">
-        <v>91784</v>
+        <v>91773</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>126858689</v>
       </c>
       <c r="B16" t="n">
-        <v>79488</v>
+        <v>79481</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>126859377</v>
       </c>
       <c r="B17" t="n">
-        <v>40040</v>
+        <v>40036</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126859418</v>
+        <v>126859410</v>
       </c>
       <c r="B18" t="n">
-        <v>91383</v>
+        <v>8458</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2772,26 +2772,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5321</v>
+        <v>101987</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Aspvedborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Heteroborips cryptographus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ratzeburg, 1837)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2892,10 +2898,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126859410</v>
+        <v>126859418</v>
       </c>
       <c r="B19" t="n">
-        <v>8461</v>
+        <v>91372</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2903,32 +2909,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101987</v>
+        <v>5321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aspvedborre</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Heteroborips cryptographus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ratzeburg, 1837)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>126858508</v>
       </c>
       <c r="B20" t="n">
-        <v>82859</v>
+        <v>82852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 1912-2023 artfynd.xlsx
+++ b/artfynd/A 1912-2023 artfynd.xlsx
@@ -2360,7 +2360,7 @@
         <v>126859596</v>
       </c>
       <c r="B15" t="n">
-        <v>91773</v>
+        <v>91784</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>126858689</v>
       </c>
       <c r="B16" t="n">
-        <v>79481</v>
+        <v>79488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>126859377</v>
       </c>
       <c r="B17" t="n">
-        <v>40036</v>
+        <v>40040</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126859410</v>
+        <v>126859418</v>
       </c>
       <c r="B18" t="n">
-        <v>8458</v>
+        <v>91383</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2772,32 +2772,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101987</v>
+        <v>5321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aspvedborre</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Heteroborips cryptographus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ratzeburg, 1837)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2898,10 +2892,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126859418</v>
+        <v>126859410</v>
       </c>
       <c r="B19" t="n">
-        <v>91372</v>
+        <v>8461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2909,26 +2903,32 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5321</v>
+        <v>101987</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Aspvedborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Heteroborips cryptographus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ratzeburg, 1837)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>126858508</v>
       </c>
       <c r="B20" t="n">
-        <v>82852</v>
+        <v>82859</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 1912-2023 artfynd.xlsx
+++ b/artfynd/A 1912-2023 artfynd.xlsx
@@ -675,60 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16798841</v>
+        <v>96905141</v>
       </c>
       <c r="B2" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4189</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östansbo vid Hundbäcken, Dlr</t>
+          <t>Östansbo, Hundbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509176.1411202319</v>
+        <v>509088</v>
       </c>
       <c r="R2" t="n">
-        <v>6663496.209875446</v>
+        <v>6663434</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,14 +766,9 @@
           <t>Lågörtgranskog</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>100-årig skog</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>gammal myrstack</t>
+          <t>barklös granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -813,52 +786,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74249883</v>
+        <v>104455663</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östansbo vid Hundbäcken, Dlr</t>
+          <t>Östansbo, Hundbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509213.9838288009</v>
+        <v>509104</v>
       </c>
       <c r="R3" t="n">
-        <v>6663342.23806499</v>
+        <v>6663400</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -885,22 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-11-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-11-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,12 +874,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>mossigt</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -935,7 +889,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>gammal granlåga # Picea abies</t>
+          <t>granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -953,15 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74249894</v>
+        <v>104455699</v>
       </c>
       <c r="B4" t="n">
-        <v>89851</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,36 +918,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5467</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östansbo vid Hundbäcken, Dlr</t>
+          <t>Östansbo, Hundbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509150.8558177771</v>
+        <v>509120</v>
       </c>
       <c r="R4" t="n">
-        <v>6663421.85664573</v>
+        <v>6663493</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1025,22 +983,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-11-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-11-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,27 +1003,17 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Blåbärsgranskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>mossigt</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>brant sluttning</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>gammal klen granlåga # Picea abies</t>
+          <t>granlåga 60 % bark kvar</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1093,37 +1031,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96640115</v>
+        <v>126859596</v>
       </c>
       <c r="B5" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1132,17 +1065,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hundbäcken, Östansbo, Dlr</t>
+          <t>Hundbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509116.3226223197</v>
+        <v>509163</v>
       </c>
       <c r="R5" t="n">
-        <v>6663249.75091619</v>
+        <v>6663533</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1166,22 +1099,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1194,11 +1127,6 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1209,57 +1137,57 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96640119</v>
+        <v>126858508</v>
       </c>
       <c r="B6" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1268,17 +1196,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hundbäcken, Östansbo, Dlr</t>
+          <t>Hundbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509116.3226223197</v>
+        <v>509182</v>
       </c>
       <c r="R6" t="n">
-        <v>6663249.75091619</v>
+        <v>6663541</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1302,22 +1230,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1332,7 +1260,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1345,39 +1273,39 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96905129</v>
+        <v>96905066</v>
       </c>
       <c r="B7" t="n">
-        <v>77959</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1408,10 +1336,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509157.4464191007</v>
+        <v>509096</v>
       </c>
       <c r="R7" t="n">
-        <v>6663582.916298064</v>
+        <v>6663775</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1441,19 +1369,9 @@
           <t>2021-10-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1469,6 +1387,21 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>inslag av tall</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>grov gran</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>grov gran</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1486,15 +1419,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96905141</v>
+        <v>96905129</v>
       </c>
       <c r="B8" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1502,21 +1430,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1797</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1529,10 +1457,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509087.8970259681</v>
+        <v>509157</v>
       </c>
       <c r="R8" t="n">
-        <v>6663434.16527954</v>
+        <v>6663583</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1562,19 +1490,9 @@
           <t>2021-10-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-10-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1590,11 +1508,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>barklös granlåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1612,19 +1525,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96905066</v>
+        <v>115297162</v>
       </c>
       <c r="B9" t="n">
-        <v>77959</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1646,22 +1554,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Östansbo, Hundbäcken, Dlr</t>
+          <t>Hundbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509096.042364086</v>
+        <v>509155</v>
       </c>
       <c r="R9" t="n">
-        <v>6663775.208665404</v>
+        <v>6663580</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1685,22 +1590,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1709,96 +1604,73 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>inslag av tall</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>grov gran</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>grov gran</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Leif Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Leif Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Artnoteringar vid kontroll av granbarkborreangre i två skogsbestånd i Ludvika kommun 2023</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96905138</v>
+        <v>126858689</v>
       </c>
       <c r="B10" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>1797</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Östansbo, Hundbäcken, Dlr</t>
+          <t>Hundbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509111.8286973929</v>
+        <v>509182</v>
       </c>
       <c r="R10" t="n">
-        <v>6663450.678150531</v>
+        <v>6663541</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1822,22 +1694,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1852,60 +1724,76 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104455663</v>
+        <v>96905138</v>
       </c>
       <c r="B11" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1913,10 +1801,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509104.4621150863</v>
+        <v>509112</v>
       </c>
       <c r="R11" t="n">
-        <v>6663400.301670977</v>
+        <v>6663450</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1943,22 +1831,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1974,21 +1852,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2006,64 +1869,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104455699</v>
+        <v>115297163</v>
       </c>
       <c r="B12" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Östansbo, Hundbäcken, Dlr</t>
+          <t>Hundbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509119.2161127821</v>
+        <v>509129</v>
       </c>
       <c r="R12" t="n">
-        <v>6663492.578037445</v>
+        <v>6663495</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2087,22 +1934,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2111,49 +1948,32 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>brant sluttning</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>granlåga 60 % bark kvar</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Leif Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Leif Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Artnoteringar vid kontroll av granbarkborreangre i två skogsbestånd i Ludvika kommun 2023</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115297163</v>
+        <v>16798841</v>
       </c>
       <c r="B13" t="n">
-        <v>94059</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2161,37 +1981,47 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>4189</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hundbäcken, Dlr</t>
+          <t>Östansbo vid Hundbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509129</v>
+        <v>509176</v>
       </c>
       <c r="R13" t="n">
-        <v>6663495</v>
+        <v>6663496</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2215,12 +2045,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2229,75 +2059,85 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>100-årig skog</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>gammal myrstack</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Artnoteringar vid kontroll av granbarkborreangre i två skogsbestånd i Ludvika kommun 2023</t>
-        </is>
-      </c>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115297162</v>
+        <v>96640115</v>
       </c>
       <c r="B14" t="n">
-        <v>78961</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1797</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hundbäcken, Dlr</t>
+          <t>Hundbäcken, Östansbo, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509155</v>
+        <v>509116</v>
       </c>
       <c r="R14" t="n">
-        <v>6663580</v>
+        <v>6663249</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2321,12 +2161,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2335,54 +2175,71 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Artnoteringar vid kontroll av granbarkborreangre i två skogsbestånd i Ludvika kommun 2023</t>
-        </is>
-      </c>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126859596</v>
+        <v>126859418</v>
       </c>
       <c r="B15" t="n">
-        <v>91784</v>
+        <v>91966</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>5321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2395,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509163</v>
+        <v>509208</v>
       </c>
       <c r="R15" t="n">
-        <v>6663533</v>
+        <v>6663371</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2430,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2440,7 +2297,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2455,12 +2312,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -2470,7 +2327,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2488,51 +2345,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126858689</v>
+        <v>74249883</v>
       </c>
       <c r="B16" t="n">
-        <v>79488</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1797</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hundbäcken, Dlr</t>
+          <t>Östansbo vid Hundbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509182</v>
+        <v>509214</v>
       </c>
       <c r="R16" t="n">
-        <v>6663541</v>
+        <v>6663342</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2556,22 +2412,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:22</t>
+          <t>2018-11-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:22</t>
+          <t>2018-11-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2586,7 +2432,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>mossigt</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2599,35 +2450,30 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>gammal granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126859377</v>
+        <v>74249894</v>
       </c>
       <c r="B17" t="n">
-        <v>40040</v>
+        <v>92398</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2635,46 +2481,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101166</v>
+        <v>5467</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hundbäcken, Dlr</t>
+          <t>Östansbo vid Hundbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509208</v>
+        <v>509151</v>
       </c>
       <c r="R17" t="n">
-        <v>6663371</v>
+        <v>6663422</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2698,22 +2537,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2018-11-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2018-11-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2726,67 +2555,72 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>mossigt</t>
+        </is>
+      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
+          <t>gammal klen granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126859418</v>
+        <v>96640119</v>
       </c>
       <c r="B18" t="n">
-        <v>91383</v>
+        <v>93233</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5321</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2795,17 +2629,17 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hundbäcken, Dlr</t>
+          <t>Hundbäcken, Östansbo, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509208</v>
+        <v>509116</v>
       </c>
       <c r="R18" t="n">
-        <v>6663371</v>
+        <v>6663249</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2829,22 +2663,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2857,78 +2681,78 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126859410</v>
+        <v>126859377</v>
       </c>
       <c r="B19" t="n">
-        <v>8461</v>
+        <v>40267</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101987</v>
+        <v>101166</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aspvedborre</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Heteroborips cryptographus</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ratzeburg, 1837)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3029,37 +2853,43 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126858508</v>
+        <v>126859410</v>
       </c>
       <c r="B20" t="n">
-        <v>82859</v>
+        <v>8466</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>101987</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Aspvedborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Heteroborips cryptographus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ratzeburg, 1837)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3067,10 +2897,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509182</v>
+        <v>509208</v>
       </c>
       <c r="R20" t="n">
-        <v>6663541</v>
+        <v>6663371</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3102,7 +2932,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3112,7 +2942,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3125,29 +2955,24 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
